--- a/sample_data/sample_Exception_Report_Amount_Differences.xlsx
+++ b/sample_data/sample_Exception_Report_Amount_Differences.xlsx
@@ -28,13 +28,13 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>20261014_063959_3b0ff9</t>
+    <t>20261014_080656_7b9a47</t>
   </si>
   <si>
     <t>Run by</t>
   </si>
   <si>
-    <t>local-user</t>
+    <t>test-user</t>
   </si>
   <si>
     <t>OPS file</t>

--- a/sample_data/sample_Exception_Report_Amount_Differences.xlsx
+++ b/sample_data/sample_Exception_Report_Amount_Differences.xlsx
@@ -28,7 +28,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>20261014_080656_7b9a47</t>
+    <t>20261015_084004_1fd7ba</t>
   </si>
   <si>
     <t>Run by</t>
